--- a/data/AREA_OPERACIONAL.xlsx
+++ b/data/AREA_OPERACIONAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://denigriscombr-my.sharepoint.com/personal/gabriel_lopes_denigris_com_br/Documents/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gflopes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="242" documentId="13_ncr:1_{F5CA61B7-4055-4F43-B809-B304BD8FD805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1FF4839-D9FD-40E0-A542-F2BF74D1F125}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B243714-17BD-41DC-96C7-88DE8597871A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARÉAS OPERACIONAL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="315">
   <si>
     <t>Região</t>
   </si>
@@ -453,9 +453,6 @@
   </si>
   <si>
     <t>JANAÍNA BROGLIO</t>
-  </si>
-  <si>
-    <t>ALEX MENDES</t>
   </si>
   <si>
     <t>CEP INICIAL</t>
@@ -1013,7 +1010,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1023,6 +1020,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1126,7 +1129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1158,6 +1161,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1167,7 +1171,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1485,7 +1491,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -1497,10 +1503,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>140</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1517,10 +1523,10 @@
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1537,10 +1543,10 @@
         <v>133</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>276</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1557,10 +1563,10 @@
         <v>84</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1577,10 +1583,10 @@
         <v>85</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1597,10 +1603,10 @@
         <v>86</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1617,10 +1623,10 @@
         <v>87</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1637,10 +1643,10 @@
         <v>88</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1657,10 +1663,10 @@
         <v>124</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1677,10 +1683,10 @@
         <v>125</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1697,10 +1703,10 @@
         <v>126</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1717,15 +1723,15 @@
         <v>89</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>139</v>
+      <c r="A13" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>132</v>
@@ -1737,15 +1743,15 @@
         <v>90</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>168</v>
-      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>139</v>
+      <c r="A14" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>132</v>
@@ -1757,15 +1763,15 @@
         <v>91</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>170</v>
-      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>139</v>
+      <c r="A15" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>132</v>
@@ -1777,15 +1783,15 @@
         <v>92</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>172</v>
-      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>139</v>
+      <c r="A16" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>132</v>
@@ -1797,15 +1803,15 @@
         <v>93</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>139</v>
+      <c r="A17" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>132</v>
@@ -1817,15 +1823,15 @@
         <v>94</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>176</v>
-      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>139</v>
+      <c r="A18" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>132</v>
@@ -1837,15 +1843,15 @@
         <v>95</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>132</v>
@@ -1857,15 +1863,15 @@
         <v>96</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>132</v>
@@ -1877,15 +1883,15 @@
         <v>97</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>132</v>
@@ -1897,15 +1903,15 @@
         <v>98</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>132</v>
@@ -1917,15 +1923,15 @@
         <v>99</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>132</v>
@@ -1937,15 +1943,15 @@
         <v>100</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>132</v>
@@ -1957,15 +1963,15 @@
         <v>101</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>132</v>
@@ -1977,15 +1983,15 @@
         <v>102</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>132</v>
@@ -1997,15 +2003,15 @@
         <v>103</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>132</v>
@@ -2017,15 +2023,15 @@
         <v>104</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>132</v>
@@ -2037,15 +2043,15 @@
         <v>28</v>
       </c>
       <c r="E28" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>132</v>
@@ -2057,15 +2063,15 @@
         <v>29</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>132</v>
@@ -2077,15 +2083,15 @@
         <v>30</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>132</v>
@@ -2097,15 +2103,15 @@
         <v>31</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>132</v>
@@ -2117,15 +2123,15 @@
         <v>105</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>132</v>
@@ -2137,15 +2143,15 @@
         <v>106</v>
       </c>
       <c r="E33" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>132</v>
@@ -2157,15 +2163,15 @@
         <v>107</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>132</v>
@@ -2177,15 +2183,15 @@
         <v>108</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>132</v>
@@ -2197,15 +2203,15 @@
         <v>109</v>
       </c>
       <c r="E36" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>132</v>
@@ -2217,15 +2223,15 @@
         <v>110</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>290</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>132</v>
@@ -2237,15 +2243,15 @@
         <v>111</v>
       </c>
       <c r="E38" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>132</v>
@@ -2257,15 +2263,15 @@
         <v>112</v>
       </c>
       <c r="E39" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>132</v>
@@ -2277,15 +2283,15 @@
         <v>113</v>
       </c>
       <c r="E40" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>132</v>
@@ -2297,15 +2303,15 @@
         <v>114</v>
       </c>
       <c r="E41" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>299</v>
-      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>139</v>
+      <c r="A42" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>132</v>
@@ -2317,15 +2323,15 @@
         <v>115</v>
       </c>
       <c r="E42" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>180</v>
-      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
-        <v>139</v>
+      <c r="A43" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>132</v>
@@ -2337,15 +2343,15 @@
         <v>116</v>
       </c>
       <c r="E43" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>182</v>
-      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>139</v>
+      <c r="A44" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>132</v>
@@ -2357,15 +2363,15 @@
         <v>117</v>
       </c>
       <c r="E44" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>184</v>
-      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
-        <v>139</v>
+      <c r="A45" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>132</v>
@@ -2377,15 +2383,15 @@
         <v>118</v>
       </c>
       <c r="E45" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>132</v>
@@ -2397,15 +2403,15 @@
         <v>119</v>
       </c>
       <c r="E46" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>132</v>
@@ -2417,15 +2423,15 @@
         <v>120</v>
       </c>
       <c r="E47" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>132</v>
@@ -2437,10 +2443,10 @@
         <v>121</v>
       </c>
       <c r="E48" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2457,10 +2463,10 @@
         <v>122</v>
       </c>
       <c r="E49" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2477,10 +2483,10 @@
         <v>123</v>
       </c>
       <c r="E50" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2490,15 +2496,15 @@
       <c r="B51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D51" s="11"/>
+      <c r="D51" s="12"/>
       <c r="E51" t="s">
+        <v>228</v>
+      </c>
+      <c r="F51" t="s">
         <v>229</v>
-      </c>
-      <c r="F51" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2508,87 +2514,87 @@
       <c r="B52" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D52" s="11"/>
+      <c r="D52" s="12"/>
       <c r="E52" t="s">
+        <v>230</v>
+      </c>
+      <c r="F52" t="s">
         <v>231</v>
       </c>
-      <c r="F52" t="s">
-        <v>232</v>
-      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>139</v>
+      <c r="A53" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D53" s="11"/>
+      <c r="D53" s="12"/>
       <c r="E53" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F53" s="4" t="s">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="12"/>
+      <c r="E54" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D54" s="11"/>
-      <c r="E54" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F54" s="4" t="s">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" s="12"/>
+      <c r="E55" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D55" s="11"/>
-      <c r="E55" s="4" t="s">
+      <c r="F55" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>156</v>
-      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
-        <v>139</v>
+      <c r="A56" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D56" s="11"/>
+      <c r="D56" s="12"/>
       <c r="E56" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2598,15 +2604,15 @@
       <c r="B57" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D57" s="11"/>
+      <c r="D57" s="12"/>
       <c r="E57" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2616,357 +2622,357 @@
       <c r="B58" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D58" s="11"/>
+      <c r="D58" s="12"/>
       <c r="E58" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D59" s="11"/>
+      <c r="D59" s="12"/>
       <c r="E59" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D60" s="11"/>
+      <c r="D60" s="12"/>
       <c r="E60" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D61" s="11"/>
+      <c r="D61" s="12"/>
       <c r="E61" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D62" s="11"/>
+      <c r="D62" s="12"/>
       <c r="E62" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D63" s="11"/>
+      <c r="D63" s="12"/>
       <c r="E63" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D64" s="11"/>
+      <c r="D64" s="12"/>
       <c r="E64" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D65" s="11"/>
+      <c r="D65" s="12"/>
       <c r="E65" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>241</v>
-      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
-        <v>139</v>
+      <c r="A66" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D66" s="11"/>
+      <c r="D66" s="12"/>
       <c r="E66" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F66" s="4" t="s">
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D67" s="12"/>
+      <c r="E67" s="4" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="4" t="s">
+      <c r="F67" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F67" s="4" t="s">
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" s="14"/>
+      <c r="E68" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" s="12"/>
+      <c r="E69" s="4" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D69" s="11"/>
-      <c r="E69" s="4" t="s">
+      <c r="F69" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F69" s="4" t="s">
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" s="12"/>
+      <c r="E70" s="4" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D70" s="11"/>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D71" s="11"/>
+      <c r="D71" s="12"/>
       <c r="E71" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D72" s="11"/>
+      <c r="D72" s="12"/>
       <c r="E72" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D73" s="11"/>
+      <c r="D73" s="12"/>
       <c r="E73" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="11"/>
+      <c r="D74" s="12"/>
       <c r="E74" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D75" s="11"/>
+      <c r="D75" s="12"/>
       <c r="E75" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D76" s="11"/>
+      <c r="D76" s="12"/>
       <c r="E76" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D77" s="11"/>
+      <c r="D77" s="12"/>
       <c r="E77" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2976,69 +2982,69 @@
       <c r="B78" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D78" s="11"/>
+      <c r="D78" s="12"/>
       <c r="E78" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D79" s="11"/>
+      <c r="D79" s="12"/>
       <c r="E79" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D80" s="11"/>
+      <c r="D80" s="12"/>
       <c r="E80" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F80" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D81" s="11"/>
+      <c r="D81" s="12"/>
       <c r="E81" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3048,33 +3054,33 @@
       <c r="B82" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D82" s="11"/>
-      <c r="E82" s="14" t="s">
+      <c r="D82" s="12"/>
+      <c r="E82" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" s="12"/>
+      <c r="E83" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D83" s="11"/>
-      <c r="E83" s="4" t="s">
+      <c r="F83" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3084,110 +3090,133 @@
       <c r="B84" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D84" s="11"/>
-      <c r="E84" s="14" t="s">
+      <c r="D84" s="12"/>
+      <c r="E84" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="F84" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="F84" s="14" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="D85" s="11"/>
+      <c r="D85" s="12"/>
       <c r="E85" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F85" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>272</v>
-      </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
-        <v>139</v>
+      <c r="A86" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D86" s="11"/>
-      <c r="E86" s="14" t="s">
+      <c r="D86" s="12"/>
+      <c r="E86" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D87" s="11"/>
+      <c r="D87" s="12"/>
       <c r="E87" t="s">
+        <v>259</v>
+      </c>
+      <c r="F87" t="s">
         <v>260</v>
-      </c>
-      <c r="F87" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D88" s="11"/>
+      <c r="D88" s="12"/>
       <c r="E88" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F88" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D89" s="11"/>
+      <c r="D89" s="12"/>
       <c r="E89" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F89" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="39">
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C70:D70"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C56:D56"/>
     <mergeCell ref="C51:D51"/>
@@ -3204,29 +3233,6 @@
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C70:D70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AREA_OPERACIONAL.xlsx
+++ b/data/AREA_OPERACIONAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gflopes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B243714-17BD-41DC-96C7-88DE8597871A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE140099-78AF-45C1-85D0-E1C41B9DADC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="316">
   <si>
     <t>Região</t>
   </si>
@@ -446,9 +446,6 @@
     <t>ZONA LIVRE</t>
   </si>
   <si>
-    <t>RENATA BELLON</t>
-  </si>
-  <si>
     <t>LEONARDO CARNEIRO</t>
   </si>
   <si>
@@ -857,9 +854,6 @@
     <t>06890-000</t>
   </si>
   <si>
-    <t>01000-000</t>
-  </si>
-  <si>
     <t>01049-999</t>
   </si>
   <si>
@@ -981,6 +975,15 @@
   </si>
   <si>
     <t>VALMIR DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>REGIANE INAMORATO</t>
+  </si>
+  <si>
+    <t>ROBSON ANDRE</t>
+  </si>
+  <si>
+    <t>01001-000</t>
   </si>
 </sst>
 </file>
@@ -1162,6 +1165,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1170,9 +1176,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1491,7 +1494,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -1503,10 +1506,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1523,10 +1526,10 @@
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>273</v>
+        <v>315</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1543,10 +1546,10 @@
         <v>133</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1563,10 +1566,10 @@
         <v>84</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1583,10 +1586,10 @@
         <v>85</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1603,10 +1606,10 @@
         <v>86</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1623,10 +1626,10 @@
         <v>87</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1643,15 +1646,15 @@
         <v>88</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>136</v>
+        <v>314</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>132</v>
@@ -1663,15 +1666,15 @@
         <v>124</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>136</v>
+        <v>314</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>132</v>
@@ -1683,15 +1686,15 @@
         <v>125</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>136</v>
+        <v>314</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>132</v>
@@ -1703,15 +1706,15 @@
         <v>126</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>136</v>
+        <v>314</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>132</v>
@@ -1723,14 +1726,14 @@
         <v>89</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1743,14 +1746,14 @@
         <v>90</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>167</v>
-      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1763,14 +1766,14 @@
         <v>91</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1783,14 +1786,14 @@
         <v>92</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>171</v>
-      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1803,14 +1806,14 @@
         <v>93</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1823,14 +1826,14 @@
         <v>94</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -1843,15 +1846,15 @@
         <v>95</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>132</v>
@@ -1863,15 +1866,15 @@
         <v>96</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>132</v>
@@ -1883,15 +1886,15 @@
         <v>97</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>132</v>
@@ -1903,15 +1906,15 @@
         <v>98</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>132</v>
@@ -1923,15 +1926,15 @@
         <v>99</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>132</v>
@@ -1943,15 +1946,15 @@
         <v>100</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>132</v>
@@ -1963,15 +1966,15 @@
         <v>101</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>132</v>
@@ -1983,15 +1986,15 @@
         <v>102</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>132</v>
@@ -2003,15 +2006,15 @@
         <v>103</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>132</v>
@@ -2023,15 +2026,15 @@
         <v>104</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>204</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>132</v>
@@ -2043,15 +2046,15 @@
         <v>28</v>
       </c>
       <c r="E28" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>132</v>
@@ -2063,15 +2066,15 @@
         <v>29</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>208</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>132</v>
@@ -2083,15 +2086,15 @@
         <v>30</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>132</v>
@@ -2103,15 +2106,15 @@
         <v>31</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>212</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>132</v>
@@ -2123,15 +2126,15 @@
         <v>105</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>132</v>
@@ -2143,15 +2146,15 @@
         <v>106</v>
       </c>
       <c r="E33" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>214</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>132</v>
@@ -2163,15 +2166,15 @@
         <v>107</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>132</v>
@@ -2183,15 +2186,15 @@
         <v>108</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>132</v>
@@ -2203,15 +2206,15 @@
         <v>109</v>
       </c>
       <c r="E36" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>132</v>
@@ -2223,15 +2226,15 @@
         <v>110</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>132</v>
@@ -2243,15 +2246,15 @@
         <v>111</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>132</v>
@@ -2263,15 +2266,15 @@
         <v>112</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>132</v>
@@ -2283,15 +2286,15 @@
         <v>113</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>132</v>
@@ -2303,14 +2306,14 @@
         <v>114</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -2323,14 +2326,14 @@
         <v>115</v>
       </c>
       <c r="E42" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>179</v>
-      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -2343,14 +2346,14 @@
         <v>116</v>
       </c>
       <c r="E43" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -2363,14 +2366,14 @@
         <v>117</v>
       </c>
       <c r="E44" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -2383,15 +2386,15 @@
         <v>118</v>
       </c>
       <c r="E45" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>132</v>
@@ -2403,15 +2406,15 @@
         <v>119</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>132</v>
@@ -2423,15 +2426,15 @@
         <v>120</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>132</v>
@@ -2443,10 +2446,10 @@
         <v>121</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2463,10 +2466,10 @@
         <v>122</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2483,717 +2486,740 @@
         <v>123</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D51" s="12"/>
+      <c r="D51" s="13"/>
       <c r="E51" t="s">
+        <v>227</v>
+      </c>
+      <c r="F51" t="s">
         <v>228</v>
-      </c>
-      <c r="F51" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D52" s="12"/>
+      <c r="D52" s="13"/>
       <c r="E52" t="s">
+        <v>229</v>
+      </c>
+      <c r="F52" t="s">
         <v>230</v>
       </c>
-      <c r="F52" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D53" s="12"/>
+      <c r="D53" s="13"/>
       <c r="E53" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F53" s="4" t="s">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="13"/>
+      <c r="E54" s="4" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="15" t="s">
+      <c r="F54" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D54" s="12"/>
-      <c r="E54" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="F54" s="4" t="s">
+      <c r="B55" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" s="13"/>
+      <c r="E55" s="4" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="15" t="s">
+      <c r="F55" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D55" s="12"/>
-      <c r="E55" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
-        <v>135</v>
-      </c>
       <c r="B56" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D56" s="12"/>
+      <c r="D56" s="13"/>
       <c r="E56" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D57" s="12"/>
+      <c r="D57" s="13"/>
       <c r="E57" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D58" s="12"/>
+      <c r="D58" s="13"/>
       <c r="E58" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D59" s="12"/>
+      <c r="D59" s="13"/>
       <c r="E59" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D60" s="12"/>
+      <c r="D60" s="13"/>
       <c r="E60" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D61" s="12"/>
+      <c r="D61" s="13"/>
       <c r="E61" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D62" s="12"/>
+      <c r="D62" s="13"/>
       <c r="E62" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D63" s="12"/>
+      <c r="D63" s="13"/>
       <c r="E63" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D64" s="12"/>
+      <c r="D64" s="13"/>
       <c r="E64" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D65" s="12"/>
+      <c r="D65" s="13"/>
       <c r="E65" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>240</v>
-      </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D66" s="12"/>
+      <c r="D66" s="13"/>
       <c r="E66" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F66" s="4" t="s">
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D67" s="13"/>
+      <c r="E67" s="4" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="15" t="s">
+      <c r="F67" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D67" s="12"/>
-      <c r="E67" s="4" t="s">
+      <c r="B68" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" s="15"/>
+      <c r="E68" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F67" s="4" t="s">
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" s="13"/>
+      <c r="E69" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="15" t="s">
+      <c r="F69" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D68" s="14"/>
-      <c r="E68" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D69" s="12"/>
-      <c r="E69" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F69" s="4" t="s">
+      <c r="B70" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" s="13"/>
+      <c r="E70" s="4" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D70" s="12"/>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D71" s="12"/>
+      <c r="D71" s="13"/>
       <c r="E71" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D72" s="12"/>
+      <c r="D72" s="13"/>
       <c r="E72" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D73" s="12"/>
+      <c r="D73" s="13"/>
       <c r="E73" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="12"/>
+      <c r="D74" s="13"/>
       <c r="E74" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D75" s="12"/>
+      <c r="D75" s="13"/>
       <c r="E75" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D76" s="12"/>
+      <c r="D76" s="13"/>
       <c r="E76" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D77" s="12"/>
+      <c r="D77" s="13"/>
       <c r="E77" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D78" s="12"/>
+      <c r="D78" s="13"/>
       <c r="E78" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D79" s="12"/>
+      <c r="D79" s="13"/>
       <c r="E79" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>253</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D80" s="12"/>
+      <c r="D80" s="13"/>
       <c r="E80" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F80" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D81" s="12"/>
+      <c r="D81" s="13"/>
       <c r="E81" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D82" s="12"/>
+      <c r="D82" s="13"/>
       <c r="E82" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" s="13"/>
+      <c r="E83" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B83" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D83" s="12"/>
-      <c r="E83" s="4" t="s">
+      <c r="F83" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>138</v>
+        <v>313</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D84" s="12"/>
+      <c r="D84" s="13"/>
       <c r="E84" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="F84" s="11" t="s">
         <v>226</v>
-      </c>
-      <c r="F84" s="11" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D85" s="12"/>
+      <c r="D85" s="13"/>
       <c r="E85" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F85" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>271</v>
-      </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="15" t="s">
+      <c r="A86" s="12" t="s">
         <v>135</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="D86" s="12"/>
+      <c r="D86" s="13"/>
       <c r="E86" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D87" s="12"/>
+      <c r="D87" s="13"/>
       <c r="E87" t="s">
+        <v>258</v>
+      </c>
+      <c r="F87" t="s">
         <v>259</v>
-      </c>
-      <c r="F87" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D88" s="12"/>
+      <c r="D88" s="13"/>
       <c r="E88" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F88" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C89" s="12" t="s">
+      <c r="C89" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D89" s="12"/>
+      <c r="D89" s="13"/>
       <c r="E89" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>223</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F89" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="39">
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C70:D70"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="C74:D74"/>
     <mergeCell ref="C75:D75"/>
@@ -3210,29 +3236,6 @@
     <mergeCell ref="C79:D79"/>
     <mergeCell ref="C80:D80"/>
     <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AREA_OPERACIONAL.xlsx
+++ b/data/AREA_OPERACIONAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gflopes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE140099-78AF-45C1-85D0-E1C41B9DADC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F98278-B2FC-4402-A2E7-04E4D4F633C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3016,7 +3016,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>3</v>
@@ -3088,7 +3088,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>313</v>
+        <v>137</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>3</v>
@@ -3197,6 +3197,29 @@
   </sheetData>
   <autoFilter ref="A1:F89" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="39">
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C70:D70"/>
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C56:D56"/>
     <mergeCell ref="C51:D51"/>
@@ -3213,29 +3236,6 @@
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AREA_OPERACIONAL.xlsx
+++ b/data/AREA_OPERACIONAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gflopes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F98278-B2FC-4402-A2E7-04E4D4F633C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9266E3B3-DC70-4A3E-881D-5DCD1BD0DEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARÉAS OPERACIONAL" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="317">
   <si>
     <t>Região</t>
   </si>
@@ -449,9 +449,6 @@
     <t>LEONARDO CARNEIRO</t>
   </si>
   <si>
-    <t>JANAÍNA BROGLIO</t>
-  </si>
-  <si>
     <t>CEP INICIAL</t>
   </si>
   <si>
@@ -984,6 +981,12 @@
   </si>
   <si>
     <t>01001-000</t>
+  </si>
+  <si>
+    <t>EDUARDO GARBIM</t>
+  </si>
+  <si>
+    <t>JANAINA BROGLIO</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1497,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -1506,10 +1509,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1526,10 +1529,10 @@
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1546,10 +1549,10 @@
         <v>133</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1566,10 +1569,10 @@
         <v>84</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1586,10 +1589,10 @@
         <v>85</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1606,10 +1609,10 @@
         <v>86</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1626,10 +1629,10 @@
         <v>87</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1646,15 +1649,15 @@
         <v>88</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>132</v>
@@ -1666,15 +1669,15 @@
         <v>124</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>132</v>
@@ -1686,15 +1689,15 @@
         <v>125</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>132</v>
@@ -1706,15 +1709,15 @@
         <v>126</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>132</v>
@@ -1726,10 +1729,10 @@
         <v>89</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1746,10 +1749,10 @@
         <v>90</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1766,10 +1769,10 @@
         <v>91</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1786,10 +1789,10 @@
         <v>92</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1806,10 +1809,10 @@
         <v>93</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1826,10 +1829,10 @@
         <v>94</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1846,15 +1849,15 @@
         <v>95</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>132</v>
@@ -1866,15 +1869,15 @@
         <v>96</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>132</v>
@@ -1886,15 +1889,15 @@
         <v>97</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>132</v>
@@ -1906,15 +1909,15 @@
         <v>98</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>132</v>
@@ -1926,15 +1929,15 @@
         <v>99</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>132</v>
@@ -1946,15 +1949,15 @@
         <v>100</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>132</v>
@@ -1966,15 +1969,15 @@
         <v>101</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>132</v>
@@ -1986,15 +1989,15 @@
         <v>102</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>132</v>
@@ -2006,15 +2009,15 @@
         <v>103</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>132</v>
@@ -2026,15 +2029,15 @@
         <v>104</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>203</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>132</v>
@@ -2046,15 +2049,15 @@
         <v>28</v>
       </c>
       <c r="E28" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>132</v>
@@ -2066,15 +2069,15 @@
         <v>29</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>132</v>
@@ -2086,15 +2089,15 @@
         <v>30</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>132</v>
@@ -2106,15 +2109,15 @@
         <v>31</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>211</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>132</v>
@@ -2126,15 +2129,15 @@
         <v>105</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>285</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>132</v>
@@ -2146,15 +2149,15 @@
         <v>106</v>
       </c>
       <c r="E33" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>132</v>
@@ -2166,15 +2169,15 @@
         <v>107</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>132</v>
@@ -2186,15 +2189,15 @@
         <v>108</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>132</v>
@@ -2206,15 +2209,15 @@
         <v>109</v>
       </c>
       <c r="E36" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>132</v>
@@ -2226,15 +2229,15 @@
         <v>110</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>132</v>
@@ -2246,15 +2249,15 @@
         <v>111</v>
       </c>
       <c r="E38" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>132</v>
@@ -2266,15 +2269,15 @@
         <v>112</v>
       </c>
       <c r="E39" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>132</v>
@@ -2286,15 +2289,15 @@
         <v>113</v>
       </c>
       <c r="E40" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>132</v>
@@ -2306,10 +2309,10 @@
         <v>114</v>
       </c>
       <c r="E41" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2326,10 +2329,10 @@
         <v>115</v>
       </c>
       <c r="E42" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2346,10 +2349,10 @@
         <v>116</v>
       </c>
       <c r="E43" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2366,10 +2369,10 @@
         <v>117</v>
       </c>
       <c r="E44" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2386,15 +2389,15 @@
         <v>118</v>
       </c>
       <c r="E45" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>183</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>132</v>
@@ -2406,15 +2409,15 @@
         <v>119</v>
       </c>
       <c r="E46" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>132</v>
@@ -2426,15 +2429,15 @@
         <v>120</v>
       </c>
       <c r="E47" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>299</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>132</v>
@@ -2446,10 +2449,10 @@
         <v>121</v>
       </c>
       <c r="E48" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2466,10 +2469,10 @@
         <v>122</v>
       </c>
       <c r="E49" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2486,10 +2489,10 @@
         <v>123</v>
       </c>
       <c r="E50" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2504,10 +2507,10 @@
       </c>
       <c r="D51" s="13"/>
       <c r="E51" t="s">
+        <v>226</v>
+      </c>
+      <c r="F51" t="s">
         <v>227</v>
-      </c>
-      <c r="F51" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2522,15 +2525,15 @@
       </c>
       <c r="D52" s="13"/>
       <c r="E52" t="s">
+        <v>228</v>
+      </c>
+      <c r="F52" t="s">
         <v>229</v>
-      </c>
-      <c r="F52" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>3</v>
@@ -2540,15 +2543,15 @@
       </c>
       <c r="D53" s="13"/>
       <c r="E53" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>3</v>
@@ -2558,15 +2561,15 @@
       </c>
       <c r="D54" s="13"/>
       <c r="E54" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>3</v>
@@ -2576,15 +2579,15 @@
       </c>
       <c r="D55" s="13"/>
       <c r="E55" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>3</v>
@@ -2594,10 +2597,10 @@
       </c>
       <c r="D56" s="13"/>
       <c r="E56" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2612,10 +2615,10 @@
       </c>
       <c r="D57" s="13"/>
       <c r="E57" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2630,15 +2633,15 @@
       </c>
       <c r="D58" s="13"/>
       <c r="E58" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>3</v>
@@ -2648,15 +2651,15 @@
       </c>
       <c r="D59" s="13"/>
       <c r="E59" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>3</v>
@@ -2666,15 +2669,15 @@
       </c>
       <c r="D60" s="13"/>
       <c r="E60" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>3</v>
@@ -2684,15 +2687,15 @@
       </c>
       <c r="D61" s="13"/>
       <c r="E61" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>3</v>
@@ -2702,15 +2705,15 @@
       </c>
       <c r="D62" s="13"/>
       <c r="E62" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>3</v>
@@ -2720,15 +2723,15 @@
       </c>
       <c r="D63" s="13"/>
       <c r="E63" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>3</v>
@@ -2738,15 +2741,15 @@
       </c>
       <c r="D64" s="13"/>
       <c r="E64" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>3</v>
@@ -2756,15 +2759,15 @@
       </c>
       <c r="D65" s="13"/>
       <c r="E65" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>3</v>
@@ -2774,15 +2777,15 @@
       </c>
       <c r="D66" s="13"/>
       <c r="E66" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>3</v>
@@ -2792,15 +2795,15 @@
       </c>
       <c r="D67" s="13"/>
       <c r="E67" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F67" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>3</v>
@@ -2810,15 +2813,15 @@
       </c>
       <c r="D68" s="15"/>
       <c r="E68" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>3</v>
@@ -2828,15 +2831,15 @@
       </c>
       <c r="D69" s="13"/>
       <c r="E69" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>3</v>
@@ -2846,15 +2849,15 @@
       </c>
       <c r="D70" s="13"/>
       <c r="E70" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F70" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>3</v>
@@ -2864,15 +2867,15 @@
       </c>
       <c r="D71" s="13"/>
       <c r="E71" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>3</v>
@@ -2882,15 +2885,15 @@
       </c>
       <c r="D72" s="13"/>
       <c r="E72" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>3</v>
@@ -2900,15 +2903,15 @@
       </c>
       <c r="D73" s="13"/>
       <c r="E73" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>3</v>
@@ -2918,15 +2921,15 @@
       </c>
       <c r="D74" s="13"/>
       <c r="E74" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>3</v>
@@ -2936,15 +2939,15 @@
       </c>
       <c r="D75" s="13"/>
       <c r="E75" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>3</v>
@@ -2954,15 +2957,15 @@
       </c>
       <c r="D76" s="13"/>
       <c r="E76" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>3</v>
@@ -2972,15 +2975,15 @@
       </c>
       <c r="D77" s="13"/>
       <c r="E77" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>3</v>
@@ -2990,15 +2993,15 @@
       </c>
       <c r="D78" s="13"/>
       <c r="E78" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>3</v>
@@ -3008,15 +3011,15 @@
       </c>
       <c r="D79" s="13"/>
       <c r="E79" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>3</v>
@@ -3026,10 +3029,10 @@
       </c>
       <c r="D80" s="13"/>
       <c r="E80" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F80" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3044,15 +3047,15 @@
       </c>
       <c r="D81" s="13"/>
       <c r="E81" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>3</v>
@@ -3062,15 +3065,15 @@
       </c>
       <c r="D82" s="13"/>
       <c r="E82" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>3</v>
@@ -3080,15 +3083,15 @@
       </c>
       <c r="D83" s="13"/>
       <c r="E83" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>3</v>
@@ -3098,15 +3101,15 @@
       </c>
       <c r="D84" s="13"/>
       <c r="E84" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="F84" s="11" t="s">
         <v>225</v>
-      </c>
-      <c r="F84" s="11" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>3</v>
@@ -3116,15 +3119,15 @@
       </c>
       <c r="D85" s="13"/>
       <c r="E85" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F85" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>3</v>
@@ -3134,15 +3137,15 @@
       </c>
       <c r="D86" s="13"/>
       <c r="E86" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>3</v>
@@ -3152,15 +3155,15 @@
       </c>
       <c r="D87" s="13"/>
       <c r="E87" t="s">
+        <v>257</v>
+      </c>
+      <c r="F87" t="s">
         <v>258</v>
-      </c>
-      <c r="F87" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>3</v>
@@ -3170,15 +3173,15 @@
       </c>
       <c r="D88" s="13"/>
       <c r="E88" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>3</v>
@@ -3188,15 +3191,38 @@
       </c>
       <c r="D89" s="13"/>
       <c r="E89" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>222</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F89" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="39">
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C70:D70"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="C74:D74"/>
     <mergeCell ref="C75:D75"/>
@@ -3213,29 +3239,6 @@
     <mergeCell ref="C79:D79"/>
     <mergeCell ref="C80:D80"/>
     <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
